--- a/AAII_Financials/Quarterly/SMPNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SMPNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="92">
   <si>
     <t>SMPNY</t>
   </si>
@@ -656,74 +656,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
-        <v>45657</v>
-      </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -760,8 +767,17 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -798,8 +814,17 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -836,8 +861,17 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -852,8 +886,11 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -890,8 +927,17 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -928,8 +974,17 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -966,8 +1021,17 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1004,8 +1068,17 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1017,8 +1090,11 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1055,8 +1131,17 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1093,8 +1178,17 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1109,8 +1203,11 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1147,8 +1244,17 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1185,8 +1291,17 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1223,8 +1338,17 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1261,8 +1385,17 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1299,8 +1432,17 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1337,8 +1479,17 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1375,8 +1526,17 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1413,8 +1573,17 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1451,8 +1620,17 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1489,8 +1667,17 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1527,8 +1714,17 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1565,8 +1761,17 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1603,8 +1808,17 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1641,8 +1855,17 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1679,8 +1902,17 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1717,51 +1949,69 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
-        <v>45657</v>
-      </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1776,8 +2026,11 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1792,122 +2045,152 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>4</v>
+      <c r="D41" s="3">
+        <v>7319000</v>
       </c>
       <c r="E41" s="3">
+        <v>7138100</v>
+      </c>
+      <c r="F41" s="3">
+        <v>8105000</v>
+      </c>
+      <c r="G41" s="3">
+        <v>6216900</v>
+      </c>
+      <c r="H41" s="3">
         <v>6862400</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8059000</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8140900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41" s="3">
+        <v>8140900</v>
+      </c>
+      <c r="M41" s="3">
         <v>9933400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>9007600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>8988700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>9377900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>11451500</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>155000</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>80600</v>
       </c>
       <c r="G42" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>767600</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>99200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>99200</v>
+      </c>
+      <c r="M42" s="3">
         <v>283800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="N42" s="3">
         <v>468700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="O42" s="3">
         <v>553300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="P42" s="3">
         <v>526600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="Q42" s="3">
         <v>530800</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
+      <c r="D43" s="3">
+        <v>261700</v>
       </c>
       <c r="E43" s="3">
+        <v>774100</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3">
+        <v>110700</v>
+      </c>
+      <c r="H43" s="3">
         <v>1049500</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>169700</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>143400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3">
+        <v>143400</v>
+      </c>
+      <c r="M43" s="3">
         <v>170000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>132500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>140700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>164900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>152200</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1944,26 +2227,35 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>13222000</v>
       </c>
       <c r="E45" s="3">
+        <v>15262500</v>
+      </c>
+      <c r="F45" s="3">
+        <v>8006800</v>
+      </c>
+      <c r="G45" s="3">
+        <v>8608900</v>
+      </c>
+      <c r="H45" s="3">
         <v>9412200</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
@@ -1982,160 +2274,205 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>4</v>
+      <c r="D46" s="3">
+        <v>20957700</v>
       </c>
       <c r="E46" s="3">
+        <v>23174700</v>
+      </c>
+      <c r="F46" s="3">
+        <v>16192400</v>
+      </c>
+      <c r="G46" s="3">
+        <v>14943600</v>
+      </c>
+      <c r="H46" s="3">
         <v>17324100</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>9030100</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8415400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="3">
+        <v>8415400</v>
+      </c>
+      <c r="M46" s="3">
         <v>10420700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>9641300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>9843300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>10229000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>12270500</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>4</v>
+      <c r="D47" s="3">
+        <v>78243600</v>
       </c>
       <c r="E47" s="3">
+        <v>78580800</v>
+      </c>
+      <c r="F47" s="3">
+        <v>77167500</v>
+      </c>
+      <c r="G47" s="3">
+        <v>77936200</v>
+      </c>
+      <c r="H47" s="3">
         <v>74199100</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>81511600</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>75533400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3">
+        <v>75533400</v>
+      </c>
+      <c r="M47" s="3">
         <v>77267900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <v>71844200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="O47" s="3">
         <v>71682700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="P47" s="3">
         <v>73782300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="Q47" s="3">
         <v>72345100</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>4</v>
+      <c r="D48" s="3">
+        <v>3967300</v>
       </c>
       <c r="E48" s="3">
+        <v>4066200</v>
+      </c>
+      <c r="F48" s="3">
+        <v>4158600</v>
+      </c>
+      <c r="G48" s="3">
+        <v>4292200</v>
+      </c>
+      <c r="H48" s="3">
         <v>4138700</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2681600</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2456700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3">
+        <v>2456700</v>
+      </c>
+      <c r="M48" s="3">
         <v>2625200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>2426700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>2504700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>2714700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>2682300</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>4</v>
+      <c r="D49" s="3">
+        <v>3666600</v>
       </c>
       <c r="E49" s="3">
+        <v>3767700</v>
+      </c>
+      <c r="F49" s="3">
+        <v>3527000</v>
+      </c>
+      <c r="G49" s="3">
+        <v>3638900</v>
+      </c>
+      <c r="H49" s="3">
         <v>3578000</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3588200</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3430800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L49" s="3">
+        <v>3430800</v>
+      </c>
+      <c r="M49" s="3">
         <v>3896400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <v>3700700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="O49" s="3">
         <v>3748200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="P49" s="3">
         <v>4085700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="Q49" s="3">
         <v>3631200</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2172,8 +2509,17 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2210,46 +2556,64 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>5297800</v>
       </c>
       <c r="E52" s="3">
+        <v>3226500</v>
+      </c>
+      <c r="F52" s="3">
+        <v>5521800</v>
+      </c>
+      <c r="G52" s="3">
+        <v>5138100</v>
+      </c>
+      <c r="H52" s="3">
         <v>2930100</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>5418700</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4679600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3">
+        <v>4679600</v>
+      </c>
+      <c r="M52" s="3">
         <v>4558600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>4255300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>5094900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>13585200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="Q52" s="3">
         <v>17363300</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2286,46 +2650,64 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>4</v>
+      <c r="D54" s="3">
+        <v>116215700</v>
       </c>
       <c r="E54" s="3">
+        <v>117000700</v>
+      </c>
+      <c r="F54" s="3">
+        <v>110525400</v>
+      </c>
+      <c r="G54" s="3">
+        <v>110017000</v>
+      </c>
+      <c r="H54" s="3">
         <v>106111900</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>105896000</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>98064700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3">
+        <v>98064700</v>
+      </c>
+      <c r="M54" s="3">
         <v>102327900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>95318200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>96455700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>108777500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>113285600</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2340,8 +2722,11 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2356,102 +2741,123 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>4</v>
+      <c r="D57" s="3">
+        <v>273200</v>
       </c>
       <c r="E57" s="3">
+        <v>573300</v>
+      </c>
+      <c r="F57" s="3">
+        <v>78500</v>
+      </c>
+      <c r="G57" s="3">
+        <v>700</v>
+      </c>
+      <c r="H57" s="3">
         <v>8200</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>21385600</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18006400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
+        <v>18006400</v>
+      </c>
+      <c r="M57" s="3">
         <v>19361800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>17660000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>16430100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>17921500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>19330000</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>4</v>
+      <c r="D58" s="3">
+        <v>6300</v>
       </c>
       <c r="E58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>641800</v>
+      </c>
+      <c r="H58" s="3">
         <v>1900</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>9500</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>11100</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
+      <c r="D59" s="3">
+        <v>491100</v>
       </c>
       <c r="E59" s="3">
+        <v>2218300</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1198500</v>
+      </c>
+      <c r="G59" s="3">
+        <v>377100</v>
+      </c>
+      <c r="H59" s="3">
         <v>2075600</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
       </c>
@@ -2470,122 +2876,158 @@
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>4</v>
+      <c r="D60" s="3">
+        <v>770500</v>
       </c>
       <c r="E60" s="3">
+        <v>2794000</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1277000</v>
+      </c>
+      <c r="G60" s="3">
+        <v>1019600</v>
+      </c>
+      <c r="H60" s="3">
         <v>2085800</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>21675600</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18399000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
+        <v>18399000</v>
+      </c>
+      <c r="M60" s="3">
         <v>19553600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>17903200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>16527800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>18255900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="Q60" s="3">
         <v>19530300</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>5878300</v>
       </c>
       <c r="E61" s="3">
+        <v>4702000</v>
+      </c>
+      <c r="F61" s="3">
+        <v>4961200</v>
+      </c>
+      <c r="G61" s="3">
+        <v>4768600</v>
+      </c>
+      <c r="H61" s="3">
         <v>5547700</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4840900</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4535700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>4535700</v>
+      </c>
+      <c r="M61" s="3">
         <v>4874800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>4583400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>4699000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>4619800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="Q61" s="3">
         <v>5055700</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4</v>
+      <c r="D62" s="3">
+        <v>71814700</v>
       </c>
       <c r="E62" s="3">
+        <v>71569500</v>
+      </c>
+      <c r="F62" s="3">
+        <v>67531300</v>
+      </c>
+      <c r="G62" s="3">
+        <v>69625000</v>
+      </c>
+      <c r="H62" s="3">
         <v>66352900</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>57767800</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>54953400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
+        <v>54953400</v>
+      </c>
+      <c r="M62" s="3">
         <v>58652400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>55849500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>58260900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>71362300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="Q62" s="3">
         <v>74714000</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2622,8 +3064,17 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2660,8 +3111,17 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2698,46 +3158,64 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>4</v>
+      <c r="D66" s="3">
+        <v>82856700</v>
       </c>
       <c r="E66" s="3">
+        <v>83725000</v>
+      </c>
+      <c r="F66" s="3">
+        <v>78106500</v>
+      </c>
+      <c r="G66" s="3">
+        <v>79822600</v>
+      </c>
+      <c r="H66" s="3">
         <v>77890100</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>84912000</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>79101700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
+        <v>79101700</v>
+      </c>
+      <c r="M66" s="3">
         <v>84027600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>79208600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>80489600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>94718700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>99877600</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2752,8 +3230,11 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2790,8 +3271,17 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2828,8 +3318,17 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2866,8 +3365,17 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2904,46 +3412,64 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
+      <c r="D72" s="3">
+        <v>27692500</v>
       </c>
       <c r="E72" s="3">
+        <v>27321900</v>
+      </c>
+      <c r="F72" s="3">
+        <v>27444400</v>
+      </c>
+      <c r="G72" s="3">
+        <v>25114200</v>
+      </c>
+      <c r="H72" s="3">
         <v>23513300</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>10528400</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8540400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
+        <v>8540400</v>
+      </c>
+      <c r="M72" s="3">
         <v>8483100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>7031500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>7064000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>7791600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>7432400</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2980,8 +3506,17 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3018,8 +3553,17 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3056,46 +3600,64 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>4</v>
+      <c r="D76" s="3">
+        <v>32607600</v>
       </c>
       <c r="E76" s="3">
+        <v>32501000</v>
+      </c>
+      <c r="F76" s="3">
+        <v>32265300</v>
+      </c>
+      <c r="G76" s="3">
+        <v>30045500</v>
+      </c>
+      <c r="H76" s="3">
         <v>28081800</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>20870000</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18856500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
+        <v>18856500</v>
+      </c>
+      <c r="M76" s="3">
         <v>18168800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>15990300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>15845800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>13950000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>13303000</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3132,51 +3694,69 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
-        <v>45657</v>
-      </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3213,8 +3793,17 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3229,8 +3818,11 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3267,8 +3859,17 @@
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3305,8 +3906,17 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3343,8 +3953,17 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3381,8 +4000,17 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3419,8 +4047,17 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3457,8 +4094,17 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3495,8 +4141,17 @@
       <c r="N89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3511,8 +4166,11 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3549,8 +4207,17 @@
       <c r="N91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3587,8 +4254,17 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3625,8 +4301,17 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3663,8 +4348,17 @@
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3679,8 +4373,11 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3717,8 +4414,17 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3755,8 +4461,17 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3793,8 +4508,17 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3831,8 +4555,17 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3869,8 +4602,17 @@
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3907,8 +4649,17 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3943,6 +4694,15 @@
         <v>4</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
